--- a/#Epstein_anonymized.xlsx
+++ b/#Epstein_anonymized.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20089,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -20782,7 +20782,7 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22235,7 +22235,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23662,7 +23662,7 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24125,7 +24125,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24816,7 +24816,7 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25511,7 +25511,7 @@
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -26778,7 +26778,7 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -27413,7 +27413,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -28126,7 +28126,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -28819,7 +28819,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -30099,7 +30099,7 @@
       </c>
       <c r="J886" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
